--- a/TestPlan_SwagLabs.xlsx
+++ b/TestPlan_SwagLabs.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Plan Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Test Cases" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Execution Tracker" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Execution Summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,7 +33,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -48,18 +49,18 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
       <sz val="10"/>
     </font>
     <font>
@@ -80,8 +81,61 @@
       <color rgb="0000B050"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -128,6 +182,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -155,22 +214,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -182,7 +237,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -203,10 +261,40 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -574,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:D11"/>
+  <dimension ref="B2:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -582,7 +670,7 @@
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>TEST PLAN – Swag Labs Web Automation</t>
@@ -590,116 +678,172 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Swag Labs (SauceDemo) Web Automation</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Application URL</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>https://www.saucedemo.com/</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Automation Tool</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Selenium WebDriver + TestNG + Java</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Report Tool</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Allure Report</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Test Author</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Mahmoud Farid</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Date Created</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="2" t="n"/>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Execution Date</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Total Test Cases</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Broken</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Pass Rate</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -715,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I29"/>
+  <dimension ref="B2:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -726,592 +870,663 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1">
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>TEST PLAN SUMMARY – Swag Labs Web Automation</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Test Case Title</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-001</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Valid Login – standard_user</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Login with correct credentials (standard_user / secret_sauce)</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>User is redirected to inventory page; URL contains 'inventory'</t>
         </is>
       </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-002</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Login – locked_out_user</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>Attempt login with a locked-out account</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Error message: 'Sorry, this user has been locked out'</t>
         </is>
       </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="7" t="n">
+      <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-003</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Login – invalid username</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Login with a non-existent username and valid password</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Error message: 'Username and password do not match'</t>
         </is>
       </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-004</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Login – invalid password</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Login with valid username and wrong password</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>Error message: 'Username and password do not match'</t>
         </is>
       </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="7" t="n">
+      <c r="B9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-005</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Login – empty username</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Submit login form with empty username field</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Error message: 'Username is required'</t>
         </is>
       </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-006</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Login – empty password</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Submit login form with empty password field</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Error message: 'Password is required'</t>
         </is>
       </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-007</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Login – empty username and password</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Submit login form with both fields empty</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>Error message: 'Username is required'</t>
         </is>
       </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-008</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Login – problem_user</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Login with problem_user account</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>User is redirected to inventory page</t>
         </is>
       </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-009</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Verify Login Page Title</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Check the browser title on the login page</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>Page title equals 'Swag Labs'</t>
         </is>
       </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="11" t="n">
+      <c r="B14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-010</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Login – performance_glitch_user</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>Login with performance_glitch_user; page may load slowly</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>User is redirected to inventory page despite delay</t>
         </is>
       </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>TC-LND-001</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Add to Cart increases badge count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Add 'Sauce Labs Backpack' and verify cart badge increments from 0 to 1</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Cart badge count equals 1</t>
         </is>
       </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>TC-LND-002</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Remove from Cart decreases badge count</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Add a product then remove it; verify badge returns to 0</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="11" t="inlineStr">
         <is>
           <t>Cart badge count equals 0 after removal</t>
         </is>
       </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>Broken</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>TC-LND-003</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Cart icon opens Cart page with selected item</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Add product and click cart icon; verify navigation and item presence</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>URL contains 'cart'; cart shows 1 item matching product name</t>
         </is>
       </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>TC-CRT-001</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Cart displays added product</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Add 'Sauce Labs Backpack' and open cart; verify item count and name</t>
         </is>
@@ -1321,37 +1536,42 @@
           <t>Cart</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>Cart shows 1 item; product name is displayed</t>
         </is>
       </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>TC-CRT-002</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Remove product decreases cart count</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Remove the product from cart and verify count drops to 0</t>
         </is>
@@ -1361,37 +1581,42 @@
           <t>Cart</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Cart item count equals 0 after removal</t>
         </is>
       </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="11" t="n">
+      <c r="B20" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>TC-CRT-003</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Checkout button navigates to Step 1</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Click Checkout button; verify URL equals checkout-step-one</t>
         </is>
@@ -1401,37 +1626,42 @@
           <t>Cart</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>URL equals checkout-step-one.html</t>
         </is>
       </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>TC-CRT-004</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Removed product not displayed in cart</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Remove product and verify it is no longer visible in cart list</t>
         </is>
@@ -1441,345 +1671,390 @@
           <t>Cart</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>isProductDisplayed() returns false for removed product</t>
         </is>
       </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="11" t="n">
+      <c r="B22" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>TC-CHK-001</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Valid checkout info navigates to Step 2</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Fill all checkout fields and click Continue; verify Step 2 appears</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>URL contains 'checkout-step-two'; summary container is visible</t>
         </is>
       </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="7" t="n">
+      <c r="B23" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>TC-CHK-002</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Missing First Name shows error</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Leave First Name empty, fill others, click Continue</t>
         </is>
       </c>
-      <c r="F23" s="13" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Error: 'Error: First Name is required'</t>
         </is>
       </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="11" t="n">
+      <c r="B24" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>TC-CHK-003</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Missing Last Name shows error</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Leave Last Name empty, fill others, click Continue</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>Error: 'Error: Last Name is required'</t>
         </is>
       </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="7" t="n">
+      <c r="B25" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>TC-CHK-004</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Missing Postal Code shows error</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Leave Postal Code empty, fill others, click Continue</t>
         </is>
       </c>
-      <c r="F25" s="13" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Error: 'Error: Postal Code is required'</t>
         </is>
       </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="11" t="n">
+      <c r="B26" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>TC-CHK-005</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Complete checkout navigates to Complete page</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Full end-to-end: login → add item → cart → checkout → finish</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="I26" s="12" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>URL equals checkout-complete.html; complete header is visible</t>
         </is>
       </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="7" t="n">
+      <c r="B27" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>TC-CHK-006</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>All fields empty shows First Name error</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Submit checkout form with all fields blank</t>
         </is>
       </c>
-      <c r="F27" s="13" t="inlineStr">
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H27" s="15" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Error: 'Error: First Name is required'</t>
         </is>
       </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="11" t="n">
+      <c r="B28" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>TC-CHK-007</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>First and Last Name missing shows error</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Submit with only postal code filled</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H28" s="15" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>Error: 'Error: First Name is required'</t>
         </is>
       </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="7" t="n">
+      <c r="B29" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>TC-CHK-008</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>First Name and Postal Code missing shows error</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Submit with only last name filled</t>
         </is>
       </c>
-      <c r="F29" s="13" t="inlineStr">
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="H29" s="15" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>Error: 'Error: First Name is required'</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1791,7 +2066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I29"/>
+  <dimension ref="B2:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1802,92 +2077,92 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1">
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>DETAILED TEST CASES – Swag Labs Web Automation</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Preconditions</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="5" ht="70" customHeight="1">
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>TC-LOG-001</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Valid Login – standard_user</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Browser is open on https://www.saucedemo.com/</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Browser open on https://www.saucedemo.com/</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>1. Enter username: standard_user
 2. Enter password: secret_sauce
 3. Click LOGIN</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Page navigates to inventory.html</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1899,39 +2174,39 @@
       </c>
     </row>
     <row r="6" ht="70" customHeight="1">
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>TC-LOG-002</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Login – locked_out_user</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>1. Enter username: locked_out_user
 2. Enter password: secret_sauce
 3. Click LOGIN</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>Error shown: 'Sorry, this user has been locked out'</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1943,39 +2218,39 @@
       </c>
     </row>
     <row r="7" ht="70" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>TC-LOG-003</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Login – invalid username</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>1. Enter username: invalid_user
 2. Enter password: secret_sauce
 3. Click LOGIN</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Error: 'Username and password do not match'</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1987,39 +2262,39 @@
       </c>
     </row>
     <row r="8" ht="70" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>TC-LOG-004</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Login – invalid password</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>1. Enter username: standard_user
 2. Enter password: wrong_password
 3. Click LOGIN</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Error: 'Username and password do not match'</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2031,39 +2306,39 @@
       </c>
     </row>
     <row r="9" ht="70" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>TC-LOG-005</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Login – empty username</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>1. Leave username blank
 2. Enter password: secret_sauce
 3. Click LOGIN</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Error: 'Username is required'</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2075,39 +2350,39 @@
       </c>
     </row>
     <row r="10" ht="70" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>TC-LOG-006</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Login – empty password</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>1. Enter username: standard_user
 2. Leave password blank
 3. Click LOGIN</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Error: 'Password is required'</t>
         </is>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2119,38 +2394,38 @@
       </c>
     </row>
     <row r="11" ht="70" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>TC-LOG-007</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Login – both fields empty</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>1. Leave both fields blank
 2. Click LOGIN</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Error: 'Username is required'</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2162,39 +2437,39 @@
       </c>
     </row>
     <row r="12" ht="70" customHeight="1">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>TC-LOG-008</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Login – problem_user</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>1. Enter username: problem_user
 2. Enter password: secret_sauce
 3. Click LOGIN</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Redirected to inventory page</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2206,37 +2481,37 @@
       </c>
     </row>
     <row r="13" ht="70" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>TC-LOG-009</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Verify Login Page Title</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>1. Check browser tab title</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Title equals 'Swag Labs'</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -2248,39 +2523,39 @@
       </c>
     </row>
     <row r="14" ht="70" customHeight="1">
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>TC-LOG-010</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Login – performance_glitch_user</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Login</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Browser is open on login page</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Browser open on login page</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>1. Enter username: performance_glitch_user
 2. Enter password: secret_sauce
 3. Click LOGIN</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Redirected to inventory page (may take extra seconds)</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2292,39 +2567,39 @@
       </c>
     </row>
     <row r="15" ht="70" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>TC-LND-001</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Add to Cart increases badge count</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Logged in as standard_user; on inventory page</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>1. Verify cart badge = 0
 2. Click 'Add to cart' for Sauce Labs Backpack
 3. Verify cart badge</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Cart badge count = 1</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2336,83 +2611,83 @@
       </c>
     </row>
     <row r="16" ht="70" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>TC-LND-002</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Remove from Cart decreases badge count</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Logged in; one item in cart</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>1. Verify badge = 1
 2. Click 'Remove' for Sauce Labs Backpack
 3. Check badge</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="11" t="inlineStr">
         <is>
           <t>Cart badge count = 0</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>Broken</t>
         </is>
       </c>
     </row>
     <row r="17" ht="70" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>TC-LND-003</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Cart icon opens Cart page</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Landing Page</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Logged in; one item added to cart</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>1. Click cart icon
 2. Wait for URL to contain 'cart'
 3. Verify item count and name</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>Cart shows 1 item; product name matches</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2424,38 +2699,38 @@
       </c>
     </row>
     <row r="18" ht="70" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>TC-CRT-001</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Cart displays added product</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Logged in; Sauce Labs Backpack added to cart; cart page open</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Logged in; Sauce Labs Backpack added; cart page open</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>1. Check item count in cart
 2. Check product name is visible</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Count = 1; product name displayed</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2467,82 +2742,82 @@
       </c>
     </row>
     <row r="19" ht="70" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>TC-CRT-002</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Remove product reduces count</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Cart page with 1 item</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>1. Confirm count = 1
 2. Click Remove
 3. Check count</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Count = 0</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="I19" s="18" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="20" ht="70" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>TC-CRT-003</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Checkout button navigates to Step 1</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Cart page with 1 item</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>1. Click Checkout button
 2. Wait for URL</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>URL = checkout-step-one.html</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2554,70 +2829,70 @@
       </c>
     </row>
     <row r="21" ht="70" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>TC-CRT-004</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Removed product not in cart</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Cart</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Cart page with 1 item</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>1. Remove product
 2. Check if product name still displayed</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>isProductDisplayed() returns false</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>Pass</t>
+      <c r="I21" s="18" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
     <row r="22" ht="70" customHeight="1">
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>TC-CHK-001</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Valid checkout info → Step 2</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>On checkout-step-one; item in cart</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>1. Enter First Name: Mohamed
 2. Last Name: Ahmed
@@ -2625,12 +2900,12 @@
 4. Click Continue</t>
         </is>
       </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="G22" s="11" t="inlineStr">
         <is>
           <t>Navigates to checkout-step-two; summary visible</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2642,39 +2917,39 @@
       </c>
     </row>
     <row r="23" ht="70" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>TC-CHK-002</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Missing First Name error</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>On checkout-step-one</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>1. Leave First Name blank
 2. Fill Last Name &amp; Postal
 3. Click Continue</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Error: 'Error: First Name is required'</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2686,27 +2961,27 @@
       </c>
     </row>
     <row r="24" ht="70" customHeight="1">
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>TC-CHK-003</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Missing Last Name error</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>On checkout-step-one</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>1. Fill First Name
 2. Leave Last Name blank
@@ -2714,12 +2989,12 @@
 4. Click Continue</t>
         </is>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="G24" s="11" t="inlineStr">
         <is>
           <t>Error: 'Error: Last Name is required'</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2731,39 +3006,39 @@
       </c>
     </row>
     <row r="25" ht="70" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>TC-CHK-004</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Missing Postal Code error</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>On checkout-step-one</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>1. Fill First &amp; Last Name
 2. Leave Postal blank
 3. Click Continue</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Error: 'Error: Postal Code is required'</t>
         </is>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2775,27 +3050,27 @@
       </c>
     </row>
     <row r="26" ht="70" customHeight="1">
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>TC-CHK-005</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="11" t="inlineStr">
         <is>
           <t>Complete checkout → Complete page</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>Logged in as standard_user</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F26" s="11" t="inlineStr">
         <is>
           <t>1. Add item to cart
 2. Go to cart → Checkout
@@ -2804,12 +3079,12 @@
 5. Click Finish</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G26" s="11" t="inlineStr">
         <is>
           <t>URL = checkout-complete.html; complete header visible</t>
         </is>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2821,38 +3096,38 @@
       </c>
     </row>
     <row r="27" ht="70" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>TC-CHK-006</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>All fields empty error</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>On checkout-step-one</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>1. Leave all fields blank
 2. Click Continue</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Error: 'Error: First Name is required'</t>
         </is>
       </c>
-      <c r="H27" s="15" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2864,38 +3139,38 @@
       </c>
     </row>
     <row r="28" ht="70" customHeight="1">
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>TC-CHK-007</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="11" t="inlineStr">
         <is>
           <t>First &amp; Last Name missing error</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>On checkout-step-one</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>1. Fill only Postal Code
 2. Click Continue</t>
         </is>
       </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="G28" s="11" t="inlineStr">
         <is>
           <t>Error: 'Error: First Name is required'</t>
         </is>
       </c>
-      <c r="H28" s="15" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2907,38 +3182,38 @@
       </c>
     </row>
     <row r="29" ht="70" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>TC-CHK-008</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>First Name &amp; Postal Code missing error</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Checkout</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>On checkout-step-one</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>1. Fill only Last Name
 2. Click Continue</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Error: 'Error: First Name is required'</t>
         </is>
       </c>
-      <c r="H29" s="15" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2951,7 +3226,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2963,7 +3238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I29"/>
+  <dimension ref="B2:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2972,812 +3247,1304 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2" ht="36" customHeight="1">
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>TEST EXECUTION TRACKER – Swag Labs</t>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>TEST EXECUTION TRACKER – Swag Labs (Run: 2026-06-26)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Executed By</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Execution Date</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Duration (ms)</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-001</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Valid Login – standard_user</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-002</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Login – locked_out_user</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr"/>
-      <c r="G6" s="11" t="inlineStr"/>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr"/>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>373</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-003</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Login – invalid username</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-004</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Login – invalid password</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="11" t="inlineStr"/>
-      <c r="H8" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>370</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-005</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Login – empty username</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>344</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-006</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Login – empty password</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr"/>
-      <c r="G10" s="11" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>345</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-007</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Login – both fields empty</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-008</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Login – problem_user</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr"/>
-      <c r="G12" s="11" t="inlineStr"/>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>353</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>TC-LOG-009</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Verify Login Page Title</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>TC-LOG-010</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Login – performance_glitch_user</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr"/>
-      <c r="G14" s="11" t="inlineStr"/>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>5373</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>TC-LND-001</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Add to Cart increases badge</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>16204</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>TC-LND-002</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Remove from Cart decreases badge</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr"/>
-      <c r="G16" s="11" t="inlineStr"/>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>Broken</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>10783</v>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>Test broken: unexpected exception during execution</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>TC-LND-003</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Cart icon opens Cart page</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>596</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>TC-CRT-001</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Cart displays added product</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr"/>
-      <c r="G18" s="11" t="inlineStr"/>
-      <c r="H18" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>5671</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>TC-CRT-002</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Remove product reduces count</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
       <c r="H19" s="18" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>639</v>
+      </c>
+      <c r="J19" s="19" t="inlineStr">
+        <is>
+          <t>Assertion failed: cart count did not reach 0 after removal</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>TC-CRT-003</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Checkout button → Step 1</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr"/>
-      <c r="G20" s="11" t="inlineStr"/>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>5766</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>TC-CRT-004</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Removed product not in cart</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>636</v>
+      </c>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>Assertion failed: product still visible in cart after remove</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>TC-CHK-001</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Valid checkout → Step 2</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr"/>
-      <c r="G22" s="11" t="inlineStr"/>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="n">
+        <v>9107</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>TC-CHK-002</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Missing First Name error</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>14095</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>TC-CHK-003</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Missing Last Name error</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr"/>
-      <c r="G24" s="11" t="inlineStr"/>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>9033</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>TC-CHK-004</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Missing Postal Code error</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>14040</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>TC-CHK-005</t>
         </is>
       </c>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Complete checkout → Complete page</t>
         </is>
       </c>
-      <c r="D26" s="10" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr"/>
-      <c r="G26" s="11" t="inlineStr"/>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>19240</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>TC-CHK-006</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>All fields empty error</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>14113</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>TC-CHK-007</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>First &amp; Last Name missing</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="10" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F28" s="12" t="inlineStr"/>
-      <c r="G28" s="11" t="inlineStr"/>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>14107</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>TC-CHK-008</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>First Name &amp; Postal Code missing</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="18" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Mahmoud Farid</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>14111</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="36" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>EXECUTION SUMMARY – 2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Total Test Cases</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Broken</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Defects Found</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>TC-CRT-002</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Remove product reduces count</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>TC-CRT-004</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Removed product not in cart</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>TC-LND-002</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Remove from Cart decreases badge</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Broken</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/TestPlan_SwagLabs.xlsx
+++ b/TestPlan_SwagLabs.xlsx
@@ -786,8 +786,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1081,7 +1082,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1156,6 +1157,10 @@
     </xf>
     <xf numFmtId="164" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2389,7 +2394,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:J29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2402,6 +2407,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="19"/>
+    </row>
     <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
         <v>145</v>
@@ -3488,7 +3496,7 @@
       <c r="I16" s="10" t="n">
         <v>10783</v>
       </c>
-      <c r="J16" s="19" t="s">
+      <c r="J16" s="20" t="s">
         <v>220</v>
       </c>
     </row>
@@ -3571,7 +3579,7 @@
       <c r="I19" s="5" t="n">
         <v>639</v>
       </c>
-      <c r="J19" s="19" t="s">
+      <c r="J19" s="20" t="s">
         <v>221</v>
       </c>
     </row>
@@ -3627,7 +3635,7 @@
       <c r="I21" s="5" t="n">
         <v>636</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="20" t="s">
         <v>223</v>
       </c>
     </row>
@@ -3893,66 +3901,66 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="22" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="23" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C8" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="24" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="25" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
@@ -3966,10 +3974,10 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="27" t="s">
         <v>183</v>
       </c>
       <c r="D13" s="18" t="s">
@@ -3977,10 +3985,10 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="28" t="s">
         <v>189</v>
       </c>
       <c r="D14" s="18" t="s">
@@ -3988,10 +3996,10 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="27" t="s">
         <v>219</v>
       </c>
       <c r="D15" s="16" t="s">
